--- a/consent_forms/038_guest_consent_form--consent_forms.xlsx
+++ b/consent_forms/038_guest_consent_form--consent_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -430,10 +440,10 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,17 +520,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>guest_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Guest Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your name</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -537,17 +547,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>guest_phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your phone number</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -564,17 +574,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your email address</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -591,17 +601,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your address</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -618,17 +628,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>emergency_contact_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Emergency Contact Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter the name of an emergency contact</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -645,17 +655,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>emergency_contact_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Emergency Contact Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter the phone number of an emergency contact</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -672,17 +682,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your doctor's name</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -699,17 +709,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your doctor's phone number</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -726,17 +736,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Medical Condition</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your medical condition</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -748,22 +758,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>treatment_options</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Treatment Options</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select your treatment options</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -780,17 +790,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>insurance_info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Insurance Info</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your insurance information</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -807,17 +817,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>medical_record_number</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Medical Record Number</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your medical record number</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -829,22 +839,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_visit_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Visit Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter the date of your doctor visit</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -856,22 +866,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_visit_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Visit Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter the time of your doctor visit</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -883,22 +893,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_visit_location</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Visit Location</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select the location of your doctor visit</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -915,17 +925,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>medication_allergies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Medication Allergies</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter any medication allergies</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -942,17 +952,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter any medical history</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -964,22 +974,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_specialties</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor Specialties</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select the doctor's specialties</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -991,22 +1001,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>doctor_office_hours</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Doctor's Office Hours</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select the doctor's office hours</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1018,22 +1028,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>payment_options</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Payment Options</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select the payment options</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1050,17 +1060,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter any additional comments</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1072,22 +1082,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please enter your date of birth</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1099,22 +1109,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Marital Status</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select your marital status</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1126,22 +1136,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>emergency_contact_relationship</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Relationship to Emergency Contact</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please select your relationship to emergency contact</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1158,17 +1168,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>&lt;string or null&gt;</t>
+          <t>Please sign below</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1183,6 +1193,433 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>treatment_options_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>treatment_options_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>treatment_options_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>doctor_visit_location_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>doctor_visit_location_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>doctor_visit_location_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>doctor_specialties_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>doctor_specialties_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>doctor_specialties_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>doctor_office_hours_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>doctor_office_hours_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>doctor_office_hours_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>payment_options_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>payment_options_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>payment_options_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>marital_status_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>marital_status_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>marital_status_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>divorced</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Divorced</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>marital_status_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>widowed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Widowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>spouse</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
